--- a/0-Config/0-Files/var_name_mapping.xlsx
+++ b/0-Config/0-Files/var_name_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maggiewang/Documents/stanford/repos/woebot/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maggiewang/Documents/stanford/repos/woebot/0-Config/0-Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E2E5D2-7508-9147-BA13-F4F2B82D93F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9029AD07-5C00-6847-B036-B0C0CD4CACE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="baseline" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="704">
   <si>
     <t>var_name</t>
   </si>
@@ -2133,6 +2133,9 @@
   </si>
   <si>
     <t>tq34</t>
+  </si>
+  <si>
+    <t>emailaddress</t>
   </si>
 </sst>
 </file>
@@ -2691,9 +2694,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2731,7 +2734,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2837,7 +2840,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2979,7 +2982,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -30387,7 +30390,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C69C1F0A-5582-4842-9906-AF7DC99E3E7B}">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.83203125" bestFit="1" customWidth="1"/>
@@ -30483,6 +30486,11 @@
         <v>572</v>
       </c>
     </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>703</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/0-Config/0-Files/var_name_mapping.xlsx
+++ b/0-Config/0-Files/var_name_mapping.xlsx
@@ -1,30 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maggiewang/Documents/stanford/repos/woebot/0-Config/0-Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9029AD07-5C00-6847-B036-B0C0CD4CACE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B76C8D1-9A2A-6044-85E9-290362FCD281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="-21100" windowWidth="30240" windowHeight="17120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="baseline" sheetId="1" r:id="rId1"/>
     <sheet name="mid" sheetId="2" r:id="rId2"/>
     <sheet name="eot" sheetId="3" r:id="rId3"/>
     <sheet name="followup" sheetId="4" r:id="rId4"/>
-    <sheet name="no_mapping" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="686">
   <si>
     <t>var_name</t>
   </si>
@@ -1694,57 +1693,6 @@
     <t>Survey #4_complete</t>
   </si>
   <si>
-    <t>participant_id</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>screen</t>
-  </si>
-  <si>
-    <t>cageaid</t>
-  </si>
-  <si>
-    <t>Randomization_complete</t>
-  </si>
-  <si>
-    <t>withdraw</t>
-  </si>
-  <si>
-    <t>age</t>
-  </si>
-  <si>
-    <t>sex</t>
-  </si>
-  <si>
-    <t>eth</t>
-  </si>
-  <si>
-    <t>race_1</t>
-  </si>
-  <si>
-    <t>race_2</t>
-  </si>
-  <si>
-    <t>race_3</t>
-  </si>
-  <si>
-    <t>race_4</t>
-  </si>
-  <si>
-    <t>race_5</t>
-  </si>
-  <si>
-    <t>race_6</t>
-  </si>
-  <si>
-    <t>race_99</t>
-  </si>
-  <si>
-    <t>race_mult</t>
-  </si>
-  <si>
     <t>eot_heavy</t>
   </si>
   <si>
@@ -2133,9 +2081,6 @@
   </si>
   <si>
     <t>tq34</t>
-  </si>
-  <si>
-    <t>emailaddress</t>
   </si>
 </sst>
 </file>
@@ -2632,9 +2577,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2990,30 +2937,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B109"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -3021,7 +2972,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -3029,7 +2980,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -3037,7 +2988,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3045,7 +2996,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3053,7 +3004,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3061,7 +3012,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3069,7 +3020,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3077,7 +3028,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3085,7 +3036,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3093,7 +3044,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -3101,7 +3052,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3109,7 +3060,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3117,7 +3068,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3815,18 +3766,18 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="B103" t="s">
-        <v>611</v>
+        <v>594</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="B104" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
@@ -3839,26 +3790,26 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>600</v>
+        <v>583</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>598</v>
+        <v>581</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>601</v>
+        <v>584</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>602</v>
+        <v>585</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
@@ -3884,10 +3835,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4293,23 +4244,23 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="B52" t="s">
-        <v>615</v>
+        <v>598</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>614</v>
+        <v>597</v>
       </c>
       <c r="B53" t="s">
-        <v>616</v>
+        <v>599</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
       <c r="B54" t="s">
         <v>255</v>
@@ -4317,7 +4268,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>661</v>
+        <v>644</v>
       </c>
       <c r="B55" t="s">
         <v>296</v>
@@ -4325,7 +4276,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>662</v>
+        <v>645</v>
       </c>
       <c r="B56" t="s">
         <v>297</v>
@@ -4333,7 +4284,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>663</v>
+        <v>646</v>
       </c>
       <c r="B57" t="s">
         <v>298</v>
@@ -4341,7 +4292,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
       <c r="B58" t="s">
         <v>299</v>
@@ -4349,7 +4300,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="B59" t="s">
         <v>300</v>
@@ -4357,7 +4308,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>666</v>
+        <v>649</v>
       </c>
       <c r="B60" t="s">
         <v>301</v>
@@ -4365,7 +4316,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
       <c r="B61" t="s">
         <v>302</v>
@@ -4373,7 +4324,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>668</v>
+        <v>651</v>
       </c>
       <c r="B62" t="s">
         <v>303</v>
@@ -4381,7 +4332,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>669</v>
+        <v>652</v>
       </c>
       <c r="B63" t="s">
         <v>304</v>
@@ -4389,7 +4340,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>670</v>
+        <v>653</v>
       </c>
       <c r="B64" t="s">
         <v>305</v>
@@ -4397,7 +4348,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="B65" t="s">
         <v>306</v>
@@ -4405,7 +4356,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>672</v>
+        <v>655</v>
       </c>
       <c r="B66" t="s">
         <v>307</v>
@@ -4435,10 +4386,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4612,82 +4563,82 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>585</v>
+        <v>568</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>575</v>
+        <v>558</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>586</v>
+        <v>569</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>576</v>
+        <v>559</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>587</v>
+        <v>570</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>577</v>
+        <v>560</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>578</v>
+        <v>561</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>589</v>
+        <v>572</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>579</v>
+        <v>562</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>580</v>
+        <v>563</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>581</v>
+        <v>564</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>592</v>
+        <v>575</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>582</v>
+        <v>565</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>583</v>
+        <v>566</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>584</v>
+        <v>567</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -4972,10 +4923,10 @@
     </row>
     <row r="68" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="C68"/>
       <c r="E68"/>
@@ -13171,10 +13122,10 @@
     </row>
     <row r="69" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="C69"/>
       <c r="E69"/>
@@ -21370,31 +21321,31 @@
     </row>
     <row r="70" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>608</v>
+        <v>591</v>
       </c>
     </row>
     <row r="71" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>617</v>
+        <v>600</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>619</v>
+        <v>602</v>
       </c>
     </row>
     <row r="72" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>620</v>
+        <v>603</v>
       </c>
     </row>
     <row r="73" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>573</v>
+        <v>556</v>
       </c>
       <c r="B73" t="s">
         <v>364</v>
@@ -21402,7 +21353,7 @@
     </row>
     <row r="74" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>649</v>
+        <v>632</v>
       </c>
       <c r="B74" t="s">
         <v>365</v>
@@ -21410,7 +21361,7 @@
     </row>
     <row r="75" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="B75" t="s">
         <v>366</v>
@@ -21418,7 +21369,7 @@
     </row>
     <row r="76" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="B76" t="s">
         <v>367</v>
@@ -21426,7 +21377,7 @@
     </row>
     <row r="77" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
       <c r="B77" t="s">
         <v>368</v>
@@ -21434,7 +21385,7 @@
     </row>
     <row r="78" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>656</v>
+        <v>639</v>
       </c>
       <c r="B78" t="s">
         <v>369</v>
@@ -21442,7 +21393,7 @@
     </row>
     <row r="79" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>659</v>
+        <v>642</v>
       </c>
       <c r="B79" t="s">
         <v>370</v>
@@ -21450,7 +21401,7 @@
     </row>
     <row r="80" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="B80" t="s">
         <v>371</v>
@@ -21458,7 +21409,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>660</v>
+        <v>643</v>
       </c>
       <c r="B81" t="s">
         <v>372</v>
@@ -21466,7 +21417,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>657</v>
+        <v>640</v>
       </c>
       <c r="B82" t="s">
         <v>373</v>
@@ -21474,7 +21425,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="B83" t="s">
         <v>374</v>
@@ -21482,7 +21433,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="B84" t="s">
         <v>375</v>
@@ -21490,7 +21441,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>654</v>
+        <v>637</v>
       </c>
       <c r="B85" t="s">
         <v>376</v>
@@ -21626,106 +21577,106 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>631</v>
+        <v>614</v>
       </c>
       <c r="B102" t="s">
-        <v>625</v>
+        <v>608</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="B103" t="s">
-        <v>626</v>
+        <v>609</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
       <c r="B104" t="s">
-        <v>627</v>
+        <v>610</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>634</v>
+        <v>617</v>
       </c>
       <c r="B105" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="B106" t="s">
-        <v>629</v>
+        <v>612</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>636</v>
+        <v>619</v>
       </c>
       <c r="B107" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="B108" t="s">
-        <v>637</v>
+        <v>620</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="B109" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>645</v>
+        <v>628</v>
       </c>
       <c r="B110" t="s">
-        <v>639</v>
+        <v>622</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="B111" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="B112" t="s">
-        <v>641</v>
+        <v>624</v>
       </c>
     </row>
     <row r="113" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>648</v>
+        <v>631</v>
       </c>
       <c r="B113" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
     </row>
     <row r="114" spans="1:1023 1025:2047 2049:3071 3073:4095 4097:5119 5121:6143 6145:7167 7169:8191 8193:9215 9217:10239 10241:11263 11265:12287 12289:13311 13313:14335 14337:15359 15361:16383" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>595</v>
+        <v>578</v>
       </c>
       <c r="B114" t="s">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="C114"/>
       <c r="E114"/>
@@ -29943,10 +29894,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -30072,122 +30023,122 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>673</v>
+        <v>656</v>
       </c>
       <c r="B17" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>674</v>
+        <v>657</v>
       </c>
       <c r="B18" t="s">
-        <v>689</v>
+        <v>672</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>675</v>
+        <v>658</v>
       </c>
       <c r="B19" t="s">
-        <v>690</v>
+        <v>673</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>676</v>
+        <v>659</v>
       </c>
       <c r="B20" t="s">
-        <v>691</v>
+        <v>674</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>677</v>
+        <v>660</v>
       </c>
       <c r="B21" t="s">
-        <v>692</v>
+        <v>675</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>678</v>
+        <v>661</v>
       </c>
       <c r="B22" t="s">
-        <v>693</v>
+        <v>676</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>679</v>
+        <v>662</v>
       </c>
       <c r="B23" t="s">
-        <v>694</v>
+        <v>677</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>680</v>
+        <v>663</v>
       </c>
       <c r="B24" t="s">
-        <v>695</v>
+        <v>678</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
       <c r="B25" t="s">
-        <v>696</v>
+        <v>679</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>682</v>
+        <v>665</v>
       </c>
       <c r="B26" t="s">
-        <v>697</v>
+        <v>680</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
       <c r="B27" t="s">
-        <v>698</v>
+        <v>681</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
       <c r="B28" t="s">
-        <v>699</v>
+        <v>682</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
       <c r="B29" t="s">
-        <v>700</v>
+        <v>683</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>686</v>
+        <v>669</v>
       </c>
       <c r="B30" t="s">
-        <v>701</v>
+        <v>684</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>687</v>
+        <v>670</v>
       </c>
       <c r="B31" t="s">
-        <v>702</v>
+        <v>685</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
@@ -30352,18 +30303,18 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>621</v>
+        <v>604</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>623</v>
+        <v>606</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>624</v>
+        <v>607</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
@@ -30380,115 +30331,6 @@
       </c>
       <c r="B55" t="s">
         <v>555</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C69C1F0A-5582-4842-9906-AF7DC99E3E7B}">
-  <dimension ref="A1:A19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="22.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>703</v>
       </c>
     </row>
   </sheetData>
